--- a/artfynd/A 59237-2022 artfynd.xlsx
+++ b/artfynd/A 59237-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59237-2022 artfynd.xlsx
+++ b/artfynd/A 59237-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89600723</v>
+        <v>89600713</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404802.0605114179</v>
+        <v>404988</v>
       </c>
       <c r="R2" t="n">
-        <v>7064748.791166293</v>
+        <v>7064830</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-09-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89600713</v>
+        <v>107258611</v>
       </c>
       <c r="B3" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,34 +787,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bränthön, Jmt</t>
+          <t>Stortjärnen Juvuln Åre, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404988.0370921008</v>
+        <v>404669</v>
       </c>
       <c r="R3" t="n">
-        <v>7064830.172781426</v>
+        <v>7064742</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +849,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,31 +874,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89600694</v>
+        <v>107258612</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,34 +897,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bränthön, Jmt</t>
+          <t>Stortjärnen Juvuln Åre, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404858.1484142526</v>
+        <v>404762</v>
       </c>
       <c r="R4" t="n">
-        <v>7064751.982763963</v>
+        <v>7064702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,22 +959,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-03-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,31 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107258627</v>
+        <v>107258613</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404882.7872797835</v>
+        <v>404910</v>
       </c>
       <c r="R5" t="n">
-        <v>7064610.999596929</v>
+        <v>7064950</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,19 +1068,9 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1147,12 +1105,7 @@
         <v>107258614</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405156.9598004741</v>
+        <v>405157</v>
       </c>
       <c r="R6" t="n">
-        <v>7064995.057829623</v>
+        <v>7064995</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,19 +1174,9 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1265,15 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107258611</v>
+        <v>107258615</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>404669.4345502218</v>
+        <v>405164</v>
       </c>
       <c r="R7" t="n">
-        <v>7064742.140532954</v>
+        <v>7064997</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,19 +1284,9 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1390,15 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107258620</v>
+        <v>107258616</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405459.0399292237</v>
+        <v>405283</v>
       </c>
       <c r="R8" t="n">
-        <v>7064562.187938925</v>
+        <v>7064954</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,19 +1390,9 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1511,15 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107258618</v>
+        <v>107258617</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405290.2108228124</v>
+        <v>405292</v>
       </c>
       <c r="R9" t="n">
-        <v>7064948.901896433</v>
+        <v>7064957</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,19 +1500,9 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1636,15 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107258613</v>
+        <v>107258618</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1565,11 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1680,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404909.4414711905</v>
+        <v>405290</v>
       </c>
       <c r="R10" t="n">
-        <v>7064950.137583015</v>
+        <v>7064949</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,19 +1610,9 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1757,15 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107258625</v>
+        <v>107258620</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405089.3698606202</v>
+        <v>405459</v>
       </c>
       <c r="R11" t="n">
-        <v>7064638.514486579</v>
+        <v>7064562</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1834,19 +1716,9 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1878,15 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107258612</v>
+        <v>107258621</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,11 +1781,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1926,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404761.5600201302</v>
+        <v>405509</v>
       </c>
       <c r="R12" t="n">
-        <v>7064702.526069053</v>
+        <v>7064549</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1959,19 +1822,9 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2003,15 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107258621</v>
+        <v>107258622</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +1887,11 @@
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2047,10 +1899,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405509.2979480934</v>
+        <v>405457</v>
       </c>
       <c r="R13" t="n">
-        <v>7064548.701083831</v>
+        <v>7064518</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2080,19 +1932,9 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2124,15 +1966,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>107258616</v>
+        <v>107258623</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2160,7 +1997,11 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2168,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405282.3660439213</v>
+        <v>405337</v>
       </c>
       <c r="R14" t="n">
-        <v>7064954.018520918</v>
+        <v>7064559</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2201,19 +2042,9 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2245,15 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>107258617</v>
+        <v>107258624</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,11 +2107,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2293,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405291.3380491704</v>
+        <v>405274</v>
       </c>
       <c r="R15" t="n">
-        <v>7064956.855750939</v>
+        <v>7064548</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2326,19 +2148,9 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2370,15 +2182,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>107258624</v>
+        <v>107258625</v>
       </c>
       <c r="B16" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2414,10 +2221,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405274.6250232566</v>
+        <v>405089</v>
       </c>
       <c r="R16" t="n">
-        <v>7064547.741572934</v>
+        <v>7064638</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2447,19 +2254,9 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2491,15 +2288,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>107258622</v>
+        <v>107258626</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,11 +2319,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2539,10 +2327,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405456.8379550768</v>
+        <v>405015</v>
       </c>
       <c r="R17" t="n">
-        <v>7064518.316163214</v>
+        <v>7064674</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2572,19 +2360,9 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2616,15 +2394,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>107258615</v>
+        <v>107258627</v>
       </c>
       <c r="B18" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2652,11 +2425,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2664,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405163.6854855178</v>
+        <v>404883</v>
       </c>
       <c r="R18" t="n">
-        <v>7064997.074616939</v>
+        <v>7064611</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2697,19 +2466,9 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">

--- a/artfynd/A 59237-2022 artfynd.xlsx
+++ b/artfynd/A 59237-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600713</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258611</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258612</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258613</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258614</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258615</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258616</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1531,6 +1571,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258617</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1641,6 +1686,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258618</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258620</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1853,6 +1908,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258621</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1963,6 +2023,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258622</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258623</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2179,6 +2249,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258624</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2285,6 +2360,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258625</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2391,6 +2471,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258626</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2497,8 +2582,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107258627</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>